--- a/TESTS/zlit_6_malenkyi_prynts.xlsx
+++ b/TESTS/zlit_6_malenkyi_prynts.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H46"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,11 @@
           <t>Тип</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ГР</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -580,7 +585,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Антуан де Сент-Екзюпері — французький льотчик і письменник що загинув під час Другої світової</t>
+          <t>Антуан де Сент-Екзюпері</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -601,6 +606,11 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -622,7 +632,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Філософська казка-притча — написана для дорослих і дітей одночасно з глибоким змістом</t>
+          <t>Філософська казка-притча</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -643,6 +653,11 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -664,7 +679,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Від льотчика що впав у пустелі і зустрів Маленького принца — оповідач-дорослий що зберіг дитячий погляд</t>
+          <t>Від льотчика що впав у пустелі і зустрів Маленького принца</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -729,6 +749,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -771,6 +796,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -790,7 +820,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Він розуміє що вона унікальна і дорога йому — не тому що красива а тому що він доглядав її і любив</t>
+          <t>Він розуміє що вона унікальна і дорога йому</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -811,6 +841,11 @@
       <c r="H7" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -832,7 +867,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Короля Пихатого Пияка Ділового Ліхтарника Географа — кожен уособлює людський порок або абсурд</t>
+          <t>Короля Пихатого Пияка Ділового Ліхтарника Географа</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -853,6 +888,11 @@
       <c r="H8" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -897,6 +937,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -939,6 +984,11 @@
           <t>single</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -948,37 +998,42 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 1)</t>
+          <t>Що намалював льотчик у дитинстві, що дорослі сприйняли неправильно?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Корабель</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Боа-констриктора, що проковтнув слона — дорослі бачили в малюнку лише капелюх</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Дерево</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Будинок</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -990,37 +1045,42 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 2)</t>
+          <t>Чому льотчик розчарувався в дорослих ще з дитинства?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Вони були жорстокими</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Вони ніколи не розуміли його малюнків і радили займатись «серйознішими» речами</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Вони не любили дітей</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Вони сміялись над ним</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1032,37 +1092,42 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Питання 4 (варіант 3)</t>
+          <t>Чому Маленький принц став для льотчика особливим, на відміну від інших дорослих?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він був дуже багатий</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Він одразу впізнав у малюнку боа зі слоном те, що там і було намальовано</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він був королем</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він подарував йому літак</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1074,37 +1139,42 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 1)</t>
+          <t>Чим, на думку Короля з першої планети, він керував?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лише своєю планетою</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Усім, включно із зорями, хоча насправді ніким не керував по-справжньому</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Лише підданими</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічим не керував</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1116,37 +1186,42 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 2)</t>
+          <t>Чому накази Короля завжди були «розумними», за його ж словами?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бо він був мудрим</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бо він наказував лише те, що так чи інакше мало статися самостійно</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо піддані самі вигадували накази</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо в нього не було підданих</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1158,37 +1233,42 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Питання 5 (варіант 3)</t>
+          <t>Що Король запропонував Маленькому принцу, коли той захотів піти?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Заборонив іти</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Призначив його міністром юстиції, аби принц залишився</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Подарував корону</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Наказав стражі його затримати</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1200,37 +1280,42 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 1)</t>
+          <t>Чого вимагав Пихатий від кожного, хто з'являвся на його планеті?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Подарунків</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Оплесків і захоплення своєю «найкращістю», хоча на планеті він був сам</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Грошей</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Покори як королю</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1242,37 +1327,42 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 2)</t>
+          <t>Чому Маленький принц швидко стомився від Пихатого?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Пихатий був злим</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Пихатий чув лише похвалу собі і не цікавився нічим іншим</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Пихатий вигнав принца</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Пихатий заснув</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1284,37 +1374,42 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Питання 6 (варіант 3)</t>
+          <t>Чому Пияк, за його ж словами, постійно пив?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Щоб бути щасливим</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Щоб забути, що йому соромно — соромно за те, що він п'є</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо це смачно</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо так наказав лікар</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1326,37 +1421,42 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 1)</t>
+          <t>У чому полягала особливість роботи Ліхтарника на його крихітній планеті?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він нічого не робив</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Через швидке обертання планети він мусив запалювати і гасити ліхтар тисячі разів на день</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він був дуже багатий</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він керував іншими планетами</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1368,37 +1468,42 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 2)</t>
+          <t>Чому Маленький принц поспівчував саме Ліхтарнику, на відміну від інших дорослих?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Не поспівчував</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бо Ліхтарник, на відміну від інших, чесно виконував свою роботу, навіть якщо вона здавалась безглуздою</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо Ліхтарник дав йому подарунок</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо Ліхтарник був королем</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1410,37 +1515,42 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Питання 7 (варіант 3)</t>
+          <t>Чому Географ порадив Маленькому принцу відвідати саме планету Земля?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Бо там найкращий клімат</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Бо Земля мала добру репутацію серед планет, хоч сам Географ нічого не досліджував особисто</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Бо там жив Король</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Бо там росли троянди</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1452,37 +1562,42 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 1)</t>
+          <t>Кого Маленький принц зустрів першим, приземлившись на Землю в пустелі?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Лиса</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Золоту змію, яка попередила, що її укус «вирішує» все назавжди</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Льотчика</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Квітку в пустелі</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1494,37 +1609,42 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 2)</t>
+          <t>Про що домовився Маленький принц зі змією наприкінці книги?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Про подорож разом</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Про те, що змія допоможе йому повернутися на свою планету через укус, бо тіло важке для такої подорожі</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Про обмін подарунками</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Нічого не домовлявся</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1536,37 +1656,42 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Питання 8 (варіант 3)</t>
+          <t>Як льотчик сприймає прощання з Маленьким принцом і укус змії наприкінці книги?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Однозначно як смерть і нічого більше</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Як сумне, але неоднозначне зникнення — тіла принца льотчик не знайшов вранці</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Як радісну подію</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Він не помітив прощання</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1703,42 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 1)</t>
+          <t>Що, за словами Лиса, означає слово «приручити»?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Підкорити</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Створити зв'язки — зробити когось єдиним у своєму роді для тебе, не схожим на жодного іншого</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Дати їжу</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Навчити трюків</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1620,37 +1750,42 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 2)</t>
+          <t>Чому Лис попросив Маленького принца приходити до нього щодня в один і той самий час?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Так зручніше Лису</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Щоб з наближенням часу зустрічі в Лиса народжувалось відчуття щастя — ритуали роблять день особливим</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Так наказали правила</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Без причини, просто звичка</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1662,37 +1797,42 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Питання 9 (варіант 3)</t>
+          <t>Як змінилось ставлення Лиса до пшеничних полів після «приручення» Маленького принца?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Не змінилось</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Золотаве колосся стало нагадувати Лису про золоте волосся принца, і тому стало для нього дорогим</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Лис почав боятися полів</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Лис залишив поля назавжди</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1704,37 +1844,42 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 1)</t>
+          <t>Яким Маленький принц став для льотчика за час, проведений у пустелі?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Просто незнайомцем</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Справжнім другом, втрата якого стала для льотчика великим горем</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Ворогом</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Випадковим знайомим</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1746,37 +1891,42 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 2)</t>
+          <t>Чому Маленький принц погодився на болючий укус змії, попри страх?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Він не розумів, що відбувається</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Це був єдиний спосіб повернутися до своєї планети й Троянди, яку він залишив без захисту</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Він хотів померти</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Змія його змусила</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1788,37 +1938,42 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Питання 10 (варіант 3)</t>
+          <t>Що, за словами книги, повинна зробити людина, дивлячись на зоряне небо після цієї історії?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Нічого особливого</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Б</t>
+          <t>Згадати, що десь там, серед зірок, є маленька планета з Трояндою і бараном — і це робить небо особливим</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>В</t>
+          <t>Полічити зорі</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Г</t>
+          <t>Зробити фото</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>single</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1843,8 +1998,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
           <t>Б</t>
@@ -1853,6 +2006,11 @@
       <c r="H32" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1877,8 +2035,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr">
         <is>
           <t>А</t>
@@ -1887,6 +2043,11 @@
       <c r="H33" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1911,8 +2072,6 @@
           <t>Хибно</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
           <t>А</t>
@@ -1921,6 +2080,11 @@
       <c r="H34" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1932,21 +2096,19 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Що символізує Троянда у «Маленькому принці»?</t>
+          <t>Троянда символізує дорогу, унікальну людину чи стосунки, за які людина несе відповідальність.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>А</t>
@@ -1955,6 +2117,11 @@
       <c r="H35" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -1966,21 +2133,19 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Що символізує подорож по планетах у творі?</t>
+          <t>Подорож Маленького принца по планетах символізує зустріч з різними людськими вадами й обмеженостями дорослих.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>А</t>
@@ -1989,6 +2154,11 @@
       <c r="H36" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2000,29 +2170,32 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Чому «Маленький принц» є водночас дитячою і дорослою книгою?</t>
+          <t>«Маленький принц» — суто дитяча книга, у якій немає сенсу для дорослих читачів.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2034,21 +2207,19 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Чому Маленький принц вирішив повернутись на свою планету?</t>
+          <t>Маленький принц вирішив повернутися на свою планету, бо турбувався про Троянду, яку залишив без захисту.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>А</t>
@@ -2057,6 +2228,11 @@
       <c r="H38" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2068,29 +2244,32 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Як Маленький принц повернувся на свою планету?</t>
+          <t>Маленький принц повернувся на свою планету на космічному кораблі, побудованому льотчиком.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>А</t>
+          <t>Б</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2102,21 +2281,19 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Яка головна ідея «Маленького принца»?</t>
+          <t>Головна ідея книги — найважливіші речі в житті часто невидимі для очей і пізнаються серцем.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Так</t>
+          <t>Правда</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Ні</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
+          <t>Хибно</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>А</t>
@@ -2125,6 +2302,11 @@
       <c r="H40" t="inlineStr">
         <is>
           <t>truefalse</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2169,6 +2351,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2211,6 +2398,11 @@
           <t>multiple</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>ГР2</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2220,27 +2412,27 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Які філософські ідеї закладені у «Маленькому принці»?</t>
+          <t>Кого Маленький принц зустрів на різних планетах перед прибуттям на Землю?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Відповідальність за тих кого любиш</t>
+          <t>Короля</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Головне невидиме для очей</t>
+          <t>Пихатого</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Зірки важливіші за людей</t>
+          <t>Лиса</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Дитячий погляд мудріший за дорослий</t>
+          <t>Ліхтарника</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2251,6 +2443,11 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2469,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>«Ми відповідальні за тих кого приручили» — і «головне невидиме для очей» — серцем бачити глибше</t>
+          <t>«Ми відповідальні за тих кого приручили»</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2293,6 +2490,11 @@
       <c r="H44" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2314,7 +2516,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Справжня любов — це відповідальність; прив'язавшись до когось ти зобов'язаний піклуватись і берегти</t>
+          <t>Справжня любов</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2335,6 +2537,11 @@
       <c r="H45" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2563,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Справжні цінності — любов дружба вірність — не можна побачити очима їх відчуває лише серце</t>
+          <t>Справжні цінності</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2377,6 +2584,11 @@
       <c r="H46" t="inlineStr">
         <is>
           <t>multiple</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>ГР2</t>
         </is>
       </c>
     </row>
